--- a/static/plot/Bell_Profile.xlsx
+++ b/static/plot/Bell_Profile.xlsx
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.465557</v>
+        <v>11.355516</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.146492</v>
+        <v>0.090086</v>
       </c>
       <c r="B3" t="n">
-        <v>18.465944</v>
+        <v>11.355754</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.292981</v>
+        <v>0.18017</v>
       </c>
       <c r="B4" t="n">
-        <v>18.467106</v>
+        <v>11.356468</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.439461</v>
+        <v>0.270249</v>
       </c>
       <c r="B5" t="n">
-        <v>18.469043</v>
+        <v>11.35766</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.585929</v>
+        <v>0.360321</v>
       </c>
       <c r="B6" t="n">
-        <v>18.471755</v>
+        <v>11.359327</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.73238</v>
+        <v>0.450382</v>
       </c>
       <c r="B7" t="n">
-        <v>18.475241</v>
+        <v>11.361471</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.878811</v>
+        <v>0.540431</v>
       </c>
       <c r="B8" t="n">
-        <v>18.479502</v>
+        <v>11.364091</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.025217</v>
+        <v>0.630464</v>
       </c>
       <c r="B9" t="n">
-        <v>18.484537</v>
+        <v>11.367187</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.171595</v>
+        <v>0.72048</v>
       </c>
       <c r="B10" t="n">
-        <v>18.490346</v>
+        <v>11.37076</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.31794</v>
+        <v>0.810476</v>
       </c>
       <c r="B11" t="n">
-        <v>18.496929</v>
+        <v>11.374808</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.464248</v>
+        <v>0.9004490000000001</v>
       </c>
       <c r="B12" t="n">
-        <v>18.504287</v>
+        <v>11.379333</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.610515</v>
+        <v>0.990397</v>
       </c>
       <c r="B13" t="n">
-        <v>18.512418</v>
+        <v>11.384333</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.756737</v>
+        <v>1.080317</v>
       </c>
       <c r="B14" t="n">
-        <v>18.521322</v>
+        <v>11.389809</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.90291</v>
+        <v>1.170207</v>
       </c>
       <c r="B15" t="n">
-        <v>18.531</v>
+        <v>11.39576</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2.04903</v>
+        <v>1.260064</v>
       </c>
       <c r="B16" t="n">
-        <v>18.541451</v>
+        <v>11.402187</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2.195092</v>
+        <v>1.349886</v>
       </c>
       <c r="B17" t="n">
-        <v>18.552674</v>
+        <v>11.409089</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.341093</v>
+        <v>1.43967</v>
       </c>
       <c r="B18" t="n">
-        <v>18.56467</v>
+        <v>11.416466</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.487028</v>
+        <v>1.529414</v>
       </c>
       <c r="B19" t="n">
-        <v>18.577437</v>
+        <v>11.424317</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2.632894</v>
+        <v>1.619116</v>
       </c>
       <c r="B20" t="n">
-        <v>18.590977</v>
+        <v>11.432643</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2.778686</v>
+        <v>1.708771</v>
       </c>
       <c r="B21" t="n">
-        <v>18.605287</v>
+        <v>11.441444</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2.924401</v>
+        <v>1.79838</v>
       </c>
       <c r="B22" t="n">
-        <v>18.620369</v>
+        <v>11.450718</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3.070034</v>
+        <v>1.887937</v>
       </c>
       <c r="B23" t="n">
-        <v>18.636221</v>
+        <v>11.460467</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.21558</v>
+        <v>1.977442</v>
       </c>
       <c r="B24" t="n">
-        <v>18.652843</v>
+        <v>11.470688</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3.361037</v>
+        <v>2.066892</v>
       </c>
       <c r="B25" t="n">
-        <v>18.670234</v>
+        <v>11.481383</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3.5064</v>
+        <v>2.156284</v>
       </c>
       <c r="B26" t="n">
-        <v>18.688395</v>
+        <v>11.492551</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3.651665</v>
+        <v>2.245615</v>
       </c>
       <c r="B27" t="n">
-        <v>18.707324</v>
+        <v>11.504192</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3.796828</v>
+        <v>2.334884</v>
       </c>
       <c r="B28" t="n">
-        <v>18.727021</v>
+        <v>11.516305</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3.941884</v>
+        <v>2.424088</v>
       </c>
       <c r="B29" t="n">
-        <v>18.747486</v>
+        <v>11.52889</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4.08683</v>
+        <v>2.513223</v>
       </c>
       <c r="B30" t="n">
-        <v>18.768717</v>
+        <v>11.541946</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4.231662</v>
+        <v>2.602288</v>
       </c>
       <c r="B31" t="n">
-        <v>18.790715</v>
+        <v>11.555474</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4.376376</v>
+        <v>2.691281</v>
       </c>
       <c r="B32" t="n">
-        <v>18.813478</v>
+        <v>11.569472</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4.520967</v>
+        <v>2.780198</v>
       </c>
       <c r="B33" t="n">
-        <v>18.837007</v>
+        <v>11.583941</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4.665431</v>
+        <v>2.869038</v>
       </c>
       <c r="B34" t="n">
-        <v>18.8613</v>
+        <v>11.59888</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4.809765</v>
+        <v>2.957797</v>
       </c>
       <c r="B35" t="n">
-        <v>18.886357</v>
+        <v>11.614289</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4.953965</v>
+        <v>3.046473</v>
       </c>
       <c r="B36" t="n">
-        <v>18.912176</v>
+        <v>11.630167</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5.098026</v>
+        <v>3.135065</v>
       </c>
       <c r="B37" t="n">
-        <v>18.938758</v>
+        <v>11.646514</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5.241944</v>
+        <v>3.223568</v>
       </c>
       <c r="B38" t="n">
-        <v>18.966102</v>
+        <v>11.663329</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5.385716</v>
+        <v>3.311982</v>
       </c>
       <c r="B39" t="n">
-        <v>18.994206</v>
+        <v>11.680612</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5.529337</v>
+        <v>3.400302</v>
       </c>
       <c r="B40" t="n">
-        <v>19.02307</v>
+        <v>11.698362</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5.672804</v>
+        <v>3.488528</v>
       </c>
       <c r="B41" t="n">
-        <v>19.052694</v>
+        <v>11.716579</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5.816111</v>
+        <v>3.576656</v>
       </c>
       <c r="B42" t="n">
-        <v>19.083075</v>
+        <v>11.735263</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5.959257</v>
+        <v>3.664684</v>
       </c>
       <c r="B43" t="n">
-        <v>19.114215</v>
+        <v>11.754412</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6.102235</v>
+        <v>3.75261</v>
       </c>
       <c r="B44" t="n">
-        <v>19.146111</v>
+        <v>11.774027</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6.245043</v>
+        <v>3.84043</v>
       </c>
       <c r="B45" t="n">
-        <v>19.178762</v>
+        <v>11.794106</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6.387676</v>
+        <v>3.928143</v>
       </c>
       <c r="B46" t="n">
-        <v>19.212169</v>
+        <v>11.81465</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6.53013</v>
+        <v>4.015746</v>
       </c>
       <c r="B47" t="n">
-        <v>19.246329</v>
+        <v>11.835657</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6.672402</v>
+        <v>4.103237</v>
       </c>
       <c r="B48" t="n">
-        <v>19.281243</v>
+        <v>11.857127</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6.814487</v>
+        <v>4.190613</v>
       </c>
       <c r="B49" t="n">
-        <v>19.316908</v>
+        <v>11.87906</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6.956381</v>
+        <v>4.277872</v>
       </c>
       <c r="B50" t="n">
-        <v>19.353324</v>
+        <v>11.901454</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>7.098081</v>
+        <v>4.365012</v>
       </c>
       <c r="B51" t="n">
-        <v>19.39049</v>
+        <v>11.92431</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>7.239582</v>
+        <v>4.452029</v>
       </c>
       <c r="B52" t="n">
-        <v>19.428406</v>
+        <v>11.947626</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>7.380881</v>
+        <v>4.538921</v>
       </c>
       <c r="B53" t="n">
-        <v>19.467069</v>
+        <v>11.971402</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>7.521973</v>
+        <v>4.625687</v>
       </c>
       <c r="B54" t="n">
-        <v>19.506478</v>
+        <v>11.995637</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>7.662855</v>
+        <v>4.712323</v>
       </c>
       <c r="B55" t="n">
-        <v>19.546634</v>
+        <v>12.020331</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7.803523</v>
+        <v>4.798828</v>
       </c>
       <c r="B56" t="n">
-        <v>19.587534</v>
+        <v>12.045483</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>7.943972</v>
+        <v>4.885198</v>
       </c>
       <c r="B57" t="n">
-        <v>19.629177</v>
+        <v>12.071092</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>8.084199</v>
+        <v>4.971431</v>
       </c>
       <c r="B58" t="n">
-        <v>19.671563</v>
+        <v>12.097157</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>8.2242</v>
+        <v>5.057526</v>
       </c>
       <c r="B59" t="n">
-        <v>19.714689</v>
+        <v>12.123678</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>8.363970999999999</v>
+        <v>5.143479</v>
       </c>
       <c r="B60" t="n">
-        <v>19.758556</v>
+        <v>12.150654</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>8.503508</v>
+        <v>5.229288</v>
       </c>
       <c r="B61" t="n">
-        <v>19.803161</v>
+        <v>12.178084</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>8.642806999999999</v>
+        <v>5.314951</v>
       </c>
       <c r="B62" t="n">
-        <v>19.848503</v>
+        <v>12.205968</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>8.781864000000001</v>
+        <v>5.400465</v>
       </c>
       <c r="B63" t="n">
-        <v>19.894582</v>
+        <v>12.234304</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>8.920676</v>
+        <v>5.485828</v>
       </c>
       <c r="B64" t="n">
-        <v>19.941395</v>
+        <v>12.263092</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>9.059238000000001</v>
+        <v>5.571038</v>
       </c>
       <c r="B65" t="n">
-        <v>19.988942</v>
+        <v>12.292332</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>9.197547</v>
+        <v>5.656092</v>
       </c>
       <c r="B66" t="n">
-        <v>20.037221</v>
+        <v>12.322021</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>9.335597999999999</v>
+        <v>5.740988</v>
       </c>
       <c r="B67" t="n">
-        <v>20.086231</v>
+        <v>12.35216</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>9.473388</v>
+        <v>5.825723</v>
       </c>
       <c r="B68" t="n">
-        <v>20.135971</v>
+        <v>12.382748</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>9.610913999999999</v>
+        <v>5.910295</v>
       </c>
       <c r="B69" t="n">
-        <v>20.186438</v>
+        <v>12.413783</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>9.74817</v>
+        <v>5.994701</v>
       </c>
       <c r="B70" t="n">
-        <v>20.237632</v>
+        <v>12.445265</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>9.885154</v>
+        <v>6.078941</v>
       </c>
       <c r="B71" t="n">
-        <v>20.289551</v>
+        <v>12.477193</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>10.021861</v>
+        <v>6.16301</v>
       </c>
       <c r="B72" t="n">
-        <v>20.342194</v>
+        <v>12.509566</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>10.158288</v>
+        <v>6.246906</v>
       </c>
       <c r="B73" t="n">
-        <v>20.395559</v>
+        <v>12.542383</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>10.294431</v>
+        <v>6.330628</v>
       </c>
       <c r="B74" t="n">
-        <v>20.449646</v>
+        <v>12.575644</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>10.430286</v>
+        <v>6.414173</v>
       </c>
       <c r="B75" t="n">
-        <v>20.504451</v>
+        <v>12.609347</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>10.565849</v>
+        <v>6.497538</v>
       </c>
       <c r="B76" t="n">
-        <v>20.559974</v>
+        <v>12.643491</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10.701117</v>
+        <v>6.580722</v>
       </c>
       <c r="B77" t="n">
-        <v>20.616213</v>
+        <v>12.678076</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10.836085</v>
+        <v>6.663722</v>
       </c>
       <c r="B78" t="n">
-        <v>20.673167</v>
+        <v>12.7131</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>10.97075</v>
+        <v>6.746535</v>
       </c>
       <c r="B79" t="n">
-        <v>20.730834</v>
+        <v>12.748563</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>11.105108</v>
+        <v>6.829159</v>
       </c>
       <c r="B80" t="n">
-        <v>20.789213</v>
+        <v>12.784463</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>11.239156</v>
+        <v>6.911593</v>
       </c>
       <c r="B81" t="n">
-        <v>20.848301</v>
+        <v>12.8208</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>11.372889</v>
+        <v>6.993833</v>
       </c>
       <c r="B82" t="n">
-        <v>20.908097</v>
+        <v>12.857572</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>11.506304</v>
+        <v>7.075877</v>
       </c>
       <c r="B83" t="n">
-        <v>20.9686</v>
+        <v>12.894778</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>11.639397</v>
+        <v>7.157724</v>
       </c>
       <c r="B84" t="n">
-        <v>21.029807</v>
+        <v>12.932418</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>11.772165</v>
+        <v>7.23937</v>
       </c>
       <c r="B85" t="n">
-        <v>21.091718</v>
+        <v>12.970491</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>11.904603</v>
+        <v>7.320814</v>
       </c>
       <c r="B86" t="n">
-        <v>21.15433</v>
+        <v>13.008994</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>12.036709</v>
+        <v>7.402053</v>
       </c>
       <c r="B87" t="n">
-        <v>21.217641</v>
+        <v>13.047928</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>12.168477</v>
+        <v>7.483085</v>
       </c>
       <c r="B88" t="n">
-        <v>21.281651</v>
+        <v>13.087291</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>12.299906</v>
+        <v>7.563908</v>
       </c>
       <c r="B89" t="n">
-        <v>21.346356</v>
+        <v>13.127082</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>12.43099</v>
+        <v>7.644519</v>
       </c>
       <c r="B90" t="n">
-        <v>21.411755</v>
+        <v>13.1673</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>12.561727</v>
+        <v>7.724916</v>
       </c>
       <c r="B91" t="n">
-        <v>21.477847</v>
+        <v>13.207943</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>12.692112</v>
+        <v>7.805098</v>
       </c>
       <c r="B92" t="n">
-        <v>21.54463</v>
+        <v>13.249012</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>12.822142</v>
+        <v>7.88506</v>
       </c>
       <c r="B93" t="n">
-        <v>21.612101</v>
+        <v>13.290503</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>12.951813</v>
+        <v>7.964803</v>
       </c>
       <c r="B94" t="n">
-        <v>21.680258</v>
+        <v>13.332418</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>13.081122</v>
+        <v>8.044321999999999</v>
       </c>
       <c r="B95" t="n">
-        <v>21.749101</v>
+        <v>13.374753</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>13.210066</v>
+        <v>8.123616999999999</v>
       </c>
       <c r="B96" t="n">
-        <v>21.818627</v>
+        <v>13.417508</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>13.338639</v>
+        <v>8.202684</v>
       </c>
       <c r="B97" t="n">
-        <v>21.888833</v>
+        <v>13.460682</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>13.46684</v>
+        <v>8.281522000000001</v>
       </c>
       <c r="B98" t="n">
-        <v>21.959719</v>
+        <v>13.504274</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>13.594664</v>
+        <v>8.360128</v>
       </c>
       <c r="B99" t="n">
-        <v>22.031281</v>
+        <v>13.548281</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>13.722108</v>
+        <v>8.438499999999999</v>
       </c>
       <c r="B100" t="n">
-        <v>22.103519</v>
+        <v>13.592704</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>13.849167</v>
+        <v>8.516636999999999</v>
       </c>
       <c r="B101" t="n">
-        <v>22.17643</v>
+        <v>13.637541</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>15.651376</v>
+        <v>9.315713000000001</v>
       </c>
       <c r="B102" t="n">
-        <v>23.213041</v>
+        <v>14.097162</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>17.453585</v>
+        <v>10.11479</v>
       </c>
       <c r="B103" t="n">
-        <v>24.241862</v>
+        <v>14.553328</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>19.255793</v>
+        <v>10.913866</v>
       </c>
       <c r="B104" t="n">
-        <v>25.262894</v>
+        <v>15.00604</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>21.058002</v>
+        <v>11.712942</v>
       </c>
       <c r="B105" t="n">
-        <v>26.276136</v>
+        <v>15.455299</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>22.86021</v>
+        <v>12.512019</v>
       </c>
       <c r="B106" t="n">
-        <v>27.281589</v>
+        <v>15.901104</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>24.662419</v>
+        <v>13.311095</v>
       </c>
       <c r="B107" t="n">
-        <v>28.279252</v>
+        <v>16.343455</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>26.464627</v>
+        <v>14.110172</v>
       </c>
       <c r="B108" t="n">
-        <v>29.269125</v>
+        <v>16.782353</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>28.266836</v>
+        <v>14.909248</v>
       </c>
       <c r="B109" t="n">
-        <v>30.251209</v>
+        <v>17.217796</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>30.069044</v>
+        <v>15.708325</v>
       </c>
       <c r="B110" t="n">
-        <v>31.225504</v>
+        <v>17.649786</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>31.871253</v>
+        <v>16.507401</v>
       </c>
       <c r="B111" t="n">
-        <v>32.192009</v>
+        <v>18.078322</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>33.673461</v>
+        <v>17.306478</v>
       </c>
       <c r="B112" t="n">
-        <v>33.150725</v>
+        <v>18.503405</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>35.47567</v>
+        <v>18.105554</v>
       </c>
       <c r="B113" t="n">
-        <v>34.101651</v>
+        <v>18.925033</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>37.277878</v>
+        <v>18.904631</v>
       </c>
       <c r="B114" t="n">
-        <v>35.044787</v>
+        <v>19.343208</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>39.080087</v>
+        <v>19.703707</v>
       </c>
       <c r="B115" t="n">
-        <v>35.980134</v>
+        <v>19.757929</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>40.882296</v>
+        <v>20.502783</v>
       </c>
       <c r="B116" t="n">
-        <v>36.907691</v>
+        <v>20.169196</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>42.684504</v>
+        <v>21.30186</v>
       </c>
       <c r="B117" t="n">
-        <v>37.827459</v>
+        <v>20.57701</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>44.486713</v>
+        <v>22.100936</v>
       </c>
       <c r="B118" t="n">
-        <v>38.739437</v>
+        <v>20.981369</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>46.288921</v>
+        <v>22.900013</v>
       </c>
       <c r="B119" t="n">
-        <v>39.643626</v>
+        <v>21.382275</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>48.09113</v>
+        <v>23.699089</v>
       </c>
       <c r="B120" t="n">
-        <v>40.540025</v>
+        <v>21.779727</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>49.893338</v>
+        <v>24.498166</v>
       </c>
       <c r="B121" t="n">
-        <v>41.428635</v>
+        <v>22.173726</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>51.695547</v>
+        <v>25.297242</v>
       </c>
       <c r="B122" t="n">
-        <v>42.309455</v>
+        <v>22.56427</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>53.497755</v>
+        <v>26.096319</v>
       </c>
       <c r="B123" t="n">
-        <v>43.182486</v>
+        <v>22.951361</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>55.299964</v>
+        <v>26.895395</v>
       </c>
       <c r="B124" t="n">
-        <v>44.047727</v>
+        <v>23.334998</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>57.102172</v>
+        <v>27.694472</v>
       </c>
       <c r="B125" t="n">
-        <v>44.905179</v>
+        <v>23.715181</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>58.904381</v>
+        <v>28.493548</v>
       </c>
       <c r="B126" t="n">
-        <v>45.754841</v>
+        <v>24.09191</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>60.70659</v>
+        <v>29.292624</v>
       </c>
       <c r="B127" t="n">
-        <v>46.596713</v>
+        <v>24.465186</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>62.508798</v>
+        <v>30.091701</v>
       </c>
       <c r="B128" t="n">
-        <v>47.430796</v>
+        <v>24.835008</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>64.311007</v>
+        <v>30.890777</v>
       </c>
       <c r="B129" t="n">
-        <v>48.25709</v>
+        <v>25.201376</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>66.113215</v>
+        <v>31.689854</v>
       </c>
       <c r="B130" t="n">
-        <v>49.075593</v>
+        <v>25.56429</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>67.915424</v>
+        <v>32.48893</v>
       </c>
       <c r="B131" t="n">
-        <v>49.886308</v>
+        <v>25.923751</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>69.71763199999999</v>
+        <v>33.288007</v>
       </c>
       <c r="B132" t="n">
-        <v>50.689233</v>
+        <v>26.279757</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>71.519841</v>
+        <v>34.087083</v>
       </c>
       <c r="B133" t="n">
-        <v>51.484368</v>
+        <v>26.63231</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>73.32204900000001</v>
+        <v>34.88616</v>
       </c>
       <c r="B134" t="n">
-        <v>52.271714</v>
+        <v>26.981409</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>75.124258</v>
+        <v>35.685236</v>
       </c>
       <c r="B135" t="n">
-        <v>53.05127</v>
+        <v>27.327055</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>76.926466</v>
+        <v>36.484313</v>
       </c>
       <c r="B136" t="n">
-        <v>53.823037</v>
+        <v>27.669246</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>78.728675</v>
+        <v>37.283389</v>
       </c>
       <c r="B137" t="n">
-        <v>54.587014</v>
+        <v>28.007984</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>80.530883</v>
+        <v>38.082465</v>
       </c>
       <c r="B138" t="n">
-        <v>55.343202</v>
+        <v>28.343268</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>82.33309199999999</v>
+        <v>38.881542</v>
       </c>
       <c r="B139" t="n">
-        <v>56.0916</v>
+        <v>28.675098</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>84.135301</v>
+        <v>39.680618</v>
       </c>
       <c r="B140" t="n">
-        <v>56.832208</v>
+        <v>29.003475</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>85.93750900000001</v>
+        <v>40.479695</v>
       </c>
       <c r="B141" t="n">
-        <v>57.565027</v>
+        <v>29.328398</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>87.739718</v>
+        <v>41.278771</v>
       </c>
       <c r="B142" t="n">
-        <v>58.290057</v>
+        <v>29.649866</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>89.541926</v>
+        <v>42.077848</v>
       </c>
       <c r="B143" t="n">
-        <v>59.007297</v>
+        <v>29.967882</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>91.34413499999999</v>
+        <v>42.876924</v>
       </c>
       <c r="B144" t="n">
-        <v>59.716747</v>
+        <v>30.282443</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>93.146343</v>
+        <v>43.676001</v>
       </c>
       <c r="B145" t="n">
-        <v>60.418408</v>
+        <v>30.593551</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>94.94855200000001</v>
+        <v>44.475077</v>
       </c>
       <c r="B146" t="n">
-        <v>61.11228</v>
+        <v>30.901204</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>96.75076</v>
+        <v>45.274153</v>
       </c>
       <c r="B147" t="n">
-        <v>61.798361</v>
+        <v>31.205404</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>98.552969</v>
+        <v>46.07323</v>
       </c>
       <c r="B148" t="n">
-        <v>62.476654</v>
+        <v>31.506151</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>100.355177</v>
+        <v>46.872306</v>
       </c>
       <c r="B149" t="n">
-        <v>63.147157</v>
+        <v>31.803443</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>102.157386</v>
+        <v>47.671383</v>
       </c>
       <c r="B150" t="n">
-        <v>63.80987</v>
+        <v>32.097282</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>103.959594</v>
+        <v>48.470459</v>
       </c>
       <c r="B151" t="n">
-        <v>64.464794</v>
+        <v>32.387667</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>105.761803</v>
+        <v>49.269536</v>
       </c>
       <c r="B152" t="n">
-        <v>65.11192800000001</v>
+        <v>32.674598</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>107.564012</v>
+        <v>50.068612</v>
       </c>
       <c r="B153" t="n">
-        <v>65.751272</v>
+        <v>32.958075</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>109.36622</v>
+        <v>50.867689</v>
       </c>
       <c r="B154" t="n">
-        <v>66.382828</v>
+        <v>33.238099</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>111.168429</v>
+        <v>51.666765</v>
       </c>
       <c r="B155" t="n">
-        <v>67.006593</v>
+        <v>33.514668</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>112.970637</v>
+        <v>52.465842</v>
       </c>
       <c r="B156" t="n">
-        <v>67.622569</v>
+        <v>33.787784</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>114.772846</v>
+        <v>53.264918</v>
       </c>
       <c r="B157" t="n">
-        <v>68.230756</v>
+        <v>34.057447</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>116.575054</v>
+        <v>54.063994</v>
       </c>
       <c r="B158" t="n">
-        <v>68.831153</v>
+        <v>34.323655</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118.377263</v>
+        <v>54.863071</v>
       </c>
       <c r="B159" t="n">
-        <v>69.42376</v>
+        <v>34.58641</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120.179471</v>
+        <v>55.662147</v>
       </c>
       <c r="B160" t="n">
-        <v>70.008578</v>
+        <v>34.84571</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121.98168</v>
+        <v>56.461224</v>
       </c>
       <c r="B161" t="n">
-        <v>70.585607</v>
+        <v>35.101558</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>123.783888</v>
+        <v>57.2603</v>
       </c>
       <c r="B162" t="n">
-        <v>71.15484499999999</v>
+        <v>35.353951</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125.586097</v>
+        <v>58.059377</v>
       </c>
       <c r="B163" t="n">
-        <v>71.716295</v>
+        <v>35.60289</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127.388306</v>
+        <v>58.858453</v>
       </c>
       <c r="B164" t="n">
-        <v>72.269955</v>
+        <v>35.848376</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129.190514</v>
+        <v>59.65753</v>
       </c>
       <c r="B165" t="n">
-        <v>72.815825</v>
+        <v>36.090408</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130.992723</v>
+        <v>60.456606</v>
       </c>
       <c r="B166" t="n">
-        <v>73.35390599999999</v>
+        <v>36.328986</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>132.794931</v>
+        <v>61.255683</v>
       </c>
       <c r="B167" t="n">
-        <v>73.884197</v>
+        <v>36.564111</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>134.59714</v>
+        <v>62.054759</v>
       </c>
       <c r="B168" t="n">
-        <v>74.40669800000001</v>
+        <v>36.795781</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>136.399348</v>
+        <v>62.853835</v>
       </c>
       <c r="B169" t="n">
-        <v>74.92141100000001</v>
+        <v>37.023998</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>138.201557</v>
+        <v>63.652912</v>
       </c>
       <c r="B170" t="n">
-        <v>75.42833299999999</v>
+        <v>37.248761</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>140.003765</v>
+        <v>64.451988</v>
       </c>
       <c r="B171" t="n">
-        <v>75.927466</v>
+        <v>37.470071</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>141.805974</v>
+        <v>65.251065</v>
       </c>
       <c r="B172" t="n">
-        <v>76.41880999999999</v>
+        <v>37.687926</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>143.608182</v>
+        <v>66.050141</v>
       </c>
       <c r="B173" t="n">
-        <v>76.90236400000001</v>
+        <v>37.902328</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>145.410391</v>
+        <v>66.84921799999999</v>
       </c>
       <c r="B174" t="n">
-        <v>77.378128</v>
+        <v>38.113276</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>147.212599</v>
+        <v>67.64829400000001</v>
       </c>
       <c r="B175" t="n">
-        <v>77.846103</v>
+        <v>38.32077</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>149.014808</v>
+        <v>68.447371</v>
       </c>
       <c r="B176" t="n">
-        <v>78.30628900000001</v>
+        <v>38.52481</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>150.817017</v>
+        <v>69.246447</v>
       </c>
       <c r="B177" t="n">
-        <v>78.758685</v>
+        <v>38.725397</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>152.619225</v>
+        <v>70.045524</v>
       </c>
       <c r="B178" t="n">
-        <v>79.20329099999999</v>
+        <v>38.92253</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>154.421434</v>
+        <v>70.8446</v>
       </c>
       <c r="B179" t="n">
-        <v>79.640108</v>
+        <v>39.116209</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>156.223642</v>
+        <v>71.643676</v>
       </c>
       <c r="B180" t="n">
-        <v>80.069135</v>
+        <v>39.306434</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>158.025851</v>
+        <v>72.442753</v>
       </c>
       <c r="B181" t="n">
-        <v>80.49037300000001</v>
+        <v>39.493206</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>159.828059</v>
+        <v>73.241829</v>
       </c>
       <c r="B182" t="n">
-        <v>80.90382099999999</v>
+        <v>39.676523</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>161.630268</v>
+        <v>74.04090600000001</v>
       </c>
       <c r="B183" t="n">
-        <v>81.30947999999999</v>
+        <v>39.856387</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>163.432476</v>
+        <v>74.83998200000001</v>
       </c>
       <c r="B184" t="n">
-        <v>81.70734899999999</v>
+        <v>40.032797</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>165.234685</v>
+        <v>75.639059</v>
       </c>
       <c r="B185" t="n">
-        <v>82.09742799999999</v>
+        <v>40.205754</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>167.036893</v>
+        <v>76.438135</v>
       </c>
       <c r="B186" t="n">
-        <v>82.479719</v>
+        <v>40.375256</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>168.839102</v>
+        <v>77.237212</v>
       </c>
       <c r="B187" t="n">
-        <v>82.854219</v>
+        <v>40.541305</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>170.641311</v>
+        <v>78.036288</v>
       </c>
       <c r="B188" t="n">
-        <v>83.22093</v>
+        <v>40.7039</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>172.443519</v>
+        <v>78.835365</v>
       </c>
       <c r="B189" t="n">
-        <v>83.579852</v>
+        <v>40.863041</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>174.245728</v>
+        <v>79.634441</v>
       </c>
       <c r="B190" t="n">
-        <v>83.930984</v>
+        <v>41.018729</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>176.047936</v>
+        <v>80.43351699999999</v>
       </c>
       <c r="B191" t="n">
-        <v>84.274326</v>
+        <v>41.170963</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>177.850145</v>
+        <v>81.23259400000001</v>
       </c>
       <c r="B192" t="n">
-        <v>84.60987900000001</v>
+        <v>41.319742</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>179.652353</v>
+        <v>82.03167000000001</v>
       </c>
       <c r="B193" t="n">
-        <v>84.937642</v>
+        <v>41.465069</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>181.454562</v>
+        <v>82.830747</v>
       </c>
       <c r="B194" t="n">
-        <v>85.257616</v>
+        <v>41.606941</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>183.25677</v>
+        <v>83.629823</v>
       </c>
       <c r="B195" t="n">
-        <v>85.5698</v>
+        <v>41.745359</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>185.058979</v>
+        <v>84.4289</v>
       </c>
       <c r="B196" t="n">
-        <v>85.874195</v>
+        <v>41.880324</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>186.861187</v>
+        <v>85.227976</v>
       </c>
       <c r="B197" t="n">
-        <v>86.1708</v>
+        <v>42.011835</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>188.663396</v>
+        <v>86.027053</v>
       </c>
       <c r="B198" t="n">
-        <v>86.459616</v>
+        <v>42.139892</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>190.465604</v>
+        <v>86.82612899999999</v>
       </c>
       <c r="B199" t="n">
-        <v>86.74064199999999</v>
+        <v>42.264496</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>192.267813</v>
+        <v>87.62520600000001</v>
       </c>
       <c r="B200" t="n">
-        <v>87.013879</v>
+        <v>42.385646</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>

--- a/static/plot/Bell_Profile.xlsx
+++ b/static/plot/Bell_Profile.xlsx
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.355516</v>
+        <v>18.465557</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -458,10 +458,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.090086</v>
+        <v>0.146492</v>
       </c>
       <c r="B3" t="n">
-        <v>11.355754</v>
+        <v>18.465944</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.18017</v>
+        <v>0.292981</v>
       </c>
       <c r="B4" t="n">
-        <v>11.356468</v>
+        <v>18.467106</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.270249</v>
+        <v>0.439461</v>
       </c>
       <c r="B5" t="n">
-        <v>11.35766</v>
+        <v>18.469043</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.360321</v>
+        <v>0.585929</v>
       </c>
       <c r="B6" t="n">
-        <v>11.359327</v>
+        <v>18.471755</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -502,10 +502,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.450382</v>
+        <v>0.73238</v>
       </c>
       <c r="B7" t="n">
-        <v>11.361471</v>
+        <v>18.475241</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.540431</v>
+        <v>0.878811</v>
       </c>
       <c r="B8" t="n">
-        <v>11.364091</v>
+        <v>18.479502</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.630464</v>
+        <v>1.025217</v>
       </c>
       <c r="B9" t="n">
-        <v>11.367187</v>
+        <v>18.484537</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.72048</v>
+        <v>1.171595</v>
       </c>
       <c r="B10" t="n">
-        <v>11.37076</v>
+        <v>18.490346</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.810476</v>
+        <v>1.31794</v>
       </c>
       <c r="B11" t="n">
-        <v>11.374808</v>
+        <v>18.496929</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -557,10 +557,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.9004490000000001</v>
+        <v>1.464248</v>
       </c>
       <c r="B12" t="n">
-        <v>11.379333</v>
+        <v>18.504287</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.990397</v>
+        <v>1.610515</v>
       </c>
       <c r="B13" t="n">
-        <v>11.384333</v>
+        <v>18.512418</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.080317</v>
+        <v>1.756737</v>
       </c>
       <c r="B14" t="n">
-        <v>11.389809</v>
+        <v>18.521322</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.170207</v>
+        <v>1.90291</v>
       </c>
       <c r="B15" t="n">
-        <v>11.39576</v>
+        <v>18.531</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.260064</v>
+        <v>2.04903</v>
       </c>
       <c r="B16" t="n">
-        <v>11.402187</v>
+        <v>18.541451</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.349886</v>
+        <v>2.195092</v>
       </c>
       <c r="B17" t="n">
-        <v>11.409089</v>
+        <v>18.552674</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1.43967</v>
+        <v>2.341093</v>
       </c>
       <c r="B18" t="n">
-        <v>11.416466</v>
+        <v>18.56467</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.529414</v>
+        <v>2.487028</v>
       </c>
       <c r="B19" t="n">
-        <v>11.424317</v>
+        <v>18.577437</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1.619116</v>
+        <v>2.632894</v>
       </c>
       <c r="B20" t="n">
-        <v>11.432643</v>
+        <v>18.590977</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -656,10 +656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1.708771</v>
+        <v>2.778686</v>
       </c>
       <c r="B21" t="n">
-        <v>11.441444</v>
+        <v>18.605287</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -667,10 +667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1.79838</v>
+        <v>2.924401</v>
       </c>
       <c r="B22" t="n">
-        <v>11.450718</v>
+        <v>18.620369</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.887937</v>
+        <v>3.070034</v>
       </c>
       <c r="B23" t="n">
-        <v>11.460467</v>
+        <v>18.636221</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.977442</v>
+        <v>3.21558</v>
       </c>
       <c r="B24" t="n">
-        <v>11.470688</v>
+        <v>18.652843</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2.066892</v>
+        <v>3.361037</v>
       </c>
       <c r="B25" t="n">
-        <v>11.481383</v>
+        <v>18.670234</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2.156284</v>
+        <v>3.5064</v>
       </c>
       <c r="B26" t="n">
-        <v>11.492551</v>
+        <v>18.688395</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2.245615</v>
+        <v>3.651665</v>
       </c>
       <c r="B27" t="n">
-        <v>11.504192</v>
+        <v>18.707324</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2.334884</v>
+        <v>3.796828</v>
       </c>
       <c r="B28" t="n">
-        <v>11.516305</v>
+        <v>18.727021</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2.424088</v>
+        <v>3.941884</v>
       </c>
       <c r="B29" t="n">
-        <v>11.52889</v>
+        <v>18.747486</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2.513223</v>
+        <v>4.08683</v>
       </c>
       <c r="B30" t="n">
-        <v>11.541946</v>
+        <v>18.768717</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2.602288</v>
+        <v>4.231662</v>
       </c>
       <c r="B31" t="n">
-        <v>11.555474</v>
+        <v>18.790715</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2.691281</v>
+        <v>4.376376</v>
       </c>
       <c r="B32" t="n">
-        <v>11.569472</v>
+        <v>18.813478</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2.780198</v>
+        <v>4.520967</v>
       </c>
       <c r="B33" t="n">
-        <v>11.583941</v>
+        <v>18.837007</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2.869038</v>
+        <v>4.665431</v>
       </c>
       <c r="B34" t="n">
-        <v>11.59888</v>
+        <v>18.8613</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -810,10 +810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2.957797</v>
+        <v>4.809765</v>
       </c>
       <c r="B35" t="n">
-        <v>11.614289</v>
+        <v>18.886357</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3.046473</v>
+        <v>4.953965</v>
       </c>
       <c r="B36" t="n">
-        <v>11.630167</v>
+        <v>18.912176</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3.135065</v>
+        <v>5.098026</v>
       </c>
       <c r="B37" t="n">
-        <v>11.646514</v>
+        <v>18.938758</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3.223568</v>
+        <v>5.241944</v>
       </c>
       <c r="B38" t="n">
-        <v>11.663329</v>
+        <v>18.966102</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3.311982</v>
+        <v>5.385716</v>
       </c>
       <c r="B39" t="n">
-        <v>11.680612</v>
+        <v>18.994206</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3.400302</v>
+        <v>5.529337</v>
       </c>
       <c r="B40" t="n">
-        <v>11.698362</v>
+        <v>19.02307</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3.488528</v>
+        <v>5.672804</v>
       </c>
       <c r="B41" t="n">
-        <v>11.716579</v>
+        <v>19.052694</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3.576656</v>
+        <v>5.816111</v>
       </c>
       <c r="B42" t="n">
-        <v>11.735263</v>
+        <v>19.083075</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3.664684</v>
+        <v>5.959257</v>
       </c>
       <c r="B43" t="n">
-        <v>11.754412</v>
+        <v>19.114215</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3.75261</v>
+        <v>6.102235</v>
       </c>
       <c r="B44" t="n">
-        <v>11.774027</v>
+        <v>19.146111</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3.84043</v>
+        <v>6.245043</v>
       </c>
       <c r="B45" t="n">
-        <v>11.794106</v>
+        <v>19.178762</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3.928143</v>
+        <v>6.387676</v>
       </c>
       <c r="B46" t="n">
-        <v>11.81465</v>
+        <v>19.212169</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4.015746</v>
+        <v>6.53013</v>
       </c>
       <c r="B47" t="n">
-        <v>11.835657</v>
+        <v>19.246329</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4.103237</v>
+        <v>6.672402</v>
       </c>
       <c r="B48" t="n">
-        <v>11.857127</v>
+        <v>19.281243</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4.190613</v>
+        <v>6.814487</v>
       </c>
       <c r="B49" t="n">
-        <v>11.87906</v>
+        <v>19.316908</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4.277872</v>
+        <v>6.956381</v>
       </c>
       <c r="B50" t="n">
-        <v>11.901454</v>
+        <v>19.353324</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4.365012</v>
+        <v>7.098081</v>
       </c>
       <c r="B51" t="n">
-        <v>11.92431</v>
+        <v>19.39049</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4.452029</v>
+        <v>7.239582</v>
       </c>
       <c r="B52" t="n">
-        <v>11.947626</v>
+        <v>19.428406</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4.538921</v>
+        <v>7.380881</v>
       </c>
       <c r="B53" t="n">
-        <v>11.971402</v>
+        <v>19.467069</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4.625687</v>
+        <v>7.521973</v>
       </c>
       <c r="B54" t="n">
-        <v>11.995637</v>
+        <v>19.506478</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4.712323</v>
+        <v>7.662855</v>
       </c>
       <c r="B55" t="n">
-        <v>12.020331</v>
+        <v>19.546634</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4.798828</v>
+        <v>7.803523</v>
       </c>
       <c r="B56" t="n">
-        <v>12.045483</v>
+        <v>19.587534</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4.885198</v>
+        <v>7.943972</v>
       </c>
       <c r="B57" t="n">
-        <v>12.071092</v>
+        <v>19.629177</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4.971431</v>
+        <v>8.084199</v>
       </c>
       <c r="B58" t="n">
-        <v>12.097157</v>
+        <v>19.671563</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5.057526</v>
+        <v>8.2242</v>
       </c>
       <c r="B59" t="n">
-        <v>12.123678</v>
+        <v>19.714689</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5.143479</v>
+        <v>8.363970999999999</v>
       </c>
       <c r="B60" t="n">
-        <v>12.150654</v>
+        <v>19.758556</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5.229288</v>
+        <v>8.503508</v>
       </c>
       <c r="B61" t="n">
-        <v>12.178084</v>
+        <v>19.803161</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5.314951</v>
+        <v>8.642806999999999</v>
       </c>
       <c r="B62" t="n">
-        <v>12.205968</v>
+        <v>19.848503</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>5.400465</v>
+        <v>8.781864000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>12.234304</v>
+        <v>19.894582</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>5.485828</v>
+        <v>8.920676</v>
       </c>
       <c r="B64" t="n">
-        <v>12.263092</v>
+        <v>19.941395</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>5.571038</v>
+        <v>9.059238000000001</v>
       </c>
       <c r="B65" t="n">
-        <v>12.292332</v>
+        <v>19.988942</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5.656092</v>
+        <v>9.197547</v>
       </c>
       <c r="B66" t="n">
-        <v>12.322021</v>
+        <v>20.037221</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>5.740988</v>
+        <v>9.335597999999999</v>
       </c>
       <c r="B67" t="n">
-        <v>12.35216</v>
+        <v>20.086231</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>5.825723</v>
+        <v>9.473388</v>
       </c>
       <c r="B68" t="n">
-        <v>12.382748</v>
+        <v>20.135971</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>5.910295</v>
+        <v>9.610913999999999</v>
       </c>
       <c r="B69" t="n">
-        <v>12.413783</v>
+        <v>20.186438</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5.994701</v>
+        <v>9.74817</v>
       </c>
       <c r="B70" t="n">
-        <v>12.445265</v>
+        <v>20.237632</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>6.078941</v>
+        <v>9.885154</v>
       </c>
       <c r="B71" t="n">
-        <v>12.477193</v>
+        <v>20.289551</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6.16301</v>
+        <v>10.021861</v>
       </c>
       <c r="B72" t="n">
-        <v>12.509566</v>
+        <v>20.342194</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>6.246906</v>
+        <v>10.158288</v>
       </c>
       <c r="B73" t="n">
-        <v>12.542383</v>
+        <v>20.395559</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6.330628</v>
+        <v>10.294431</v>
       </c>
       <c r="B74" t="n">
-        <v>12.575644</v>
+        <v>20.449646</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>6.414173</v>
+        <v>10.430286</v>
       </c>
       <c r="B75" t="n">
-        <v>12.609347</v>
+        <v>20.504451</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6.497538</v>
+        <v>10.565849</v>
       </c>
       <c r="B76" t="n">
-        <v>12.643491</v>
+        <v>20.559974</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6.580722</v>
+        <v>10.701117</v>
       </c>
       <c r="B77" t="n">
-        <v>12.678076</v>
+        <v>20.616213</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1283,10 +1283,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>6.663722</v>
+        <v>10.836085</v>
       </c>
       <c r="B78" t="n">
-        <v>12.7131</v>
+        <v>20.673167</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>6.746535</v>
+        <v>10.97075</v>
       </c>
       <c r="B79" t="n">
-        <v>12.748563</v>
+        <v>20.730834</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6.829159</v>
+        <v>11.105108</v>
       </c>
       <c r="B80" t="n">
-        <v>12.784463</v>
+        <v>20.789213</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6.911593</v>
+        <v>11.239156</v>
       </c>
       <c r="B81" t="n">
-        <v>12.8208</v>
+        <v>20.848301</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6.993833</v>
+        <v>11.372889</v>
       </c>
       <c r="B82" t="n">
-        <v>12.857572</v>
+        <v>20.908097</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7.075877</v>
+        <v>11.506304</v>
       </c>
       <c r="B83" t="n">
-        <v>12.894778</v>
+        <v>20.9686</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>7.157724</v>
+        <v>11.639397</v>
       </c>
       <c r="B84" t="n">
-        <v>12.932418</v>
+        <v>21.029807</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>7.23937</v>
+        <v>11.772165</v>
       </c>
       <c r="B85" t="n">
-        <v>12.970491</v>
+        <v>21.091718</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7.320814</v>
+        <v>11.904603</v>
       </c>
       <c r="B86" t="n">
-        <v>13.008994</v>
+        <v>21.15433</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>7.402053</v>
+        <v>12.036709</v>
       </c>
       <c r="B87" t="n">
-        <v>13.047928</v>
+        <v>21.217641</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>7.483085</v>
+        <v>12.168477</v>
       </c>
       <c r="B88" t="n">
-        <v>13.087291</v>
+        <v>21.281651</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>7.563908</v>
+        <v>12.299906</v>
       </c>
       <c r="B89" t="n">
-        <v>13.127082</v>
+        <v>21.346356</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>7.644519</v>
+        <v>12.43099</v>
       </c>
       <c r="B90" t="n">
-        <v>13.1673</v>
+        <v>21.411755</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>7.724916</v>
+        <v>12.561727</v>
       </c>
       <c r="B91" t="n">
-        <v>13.207943</v>
+        <v>21.477847</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>7.805098</v>
+        <v>12.692112</v>
       </c>
       <c r="B92" t="n">
-        <v>13.249012</v>
+        <v>21.54463</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7.88506</v>
+        <v>12.822142</v>
       </c>
       <c r="B93" t="n">
-        <v>13.290503</v>
+        <v>21.612101</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7.964803</v>
+        <v>12.951813</v>
       </c>
       <c r="B94" t="n">
-        <v>13.332418</v>
+        <v>21.680258</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>8.044321999999999</v>
+        <v>13.081122</v>
       </c>
       <c r="B95" t="n">
-        <v>13.374753</v>
+        <v>21.749101</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>8.123616999999999</v>
+        <v>13.210066</v>
       </c>
       <c r="B96" t="n">
-        <v>13.417508</v>
+        <v>21.818627</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>8.202684</v>
+        <v>13.338639</v>
       </c>
       <c r="B97" t="n">
-        <v>13.460682</v>
+        <v>21.888833</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>8.281522000000001</v>
+        <v>13.46684</v>
       </c>
       <c r="B98" t="n">
-        <v>13.504274</v>
+        <v>21.959719</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>8.360128</v>
+        <v>13.594664</v>
       </c>
       <c r="B99" t="n">
-        <v>13.548281</v>
+        <v>22.031281</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>8.438499999999999</v>
+        <v>13.722108</v>
       </c>
       <c r="B100" t="n">
-        <v>13.592704</v>
+        <v>22.103519</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>8.516636999999999</v>
+        <v>13.849167</v>
       </c>
       <c r="B101" t="n">
-        <v>13.637541</v>
+        <v>22.17643</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>9.315713000000001</v>
+        <v>15.651376</v>
       </c>
       <c r="B102" t="n">
-        <v>14.097162</v>
+        <v>23.213041</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>10.11479</v>
+        <v>17.453585</v>
       </c>
       <c r="B103" t="n">
-        <v>14.553328</v>
+        <v>24.241862</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>10.913866</v>
+        <v>19.255793</v>
       </c>
       <c r="B104" t="n">
-        <v>15.00604</v>
+        <v>25.262894</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>11.712942</v>
+        <v>21.058002</v>
       </c>
       <c r="B105" t="n">
-        <v>15.455299</v>
+        <v>26.276136</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>12.512019</v>
+        <v>22.86021</v>
       </c>
       <c r="B106" t="n">
-        <v>15.901104</v>
+        <v>27.281589</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>13.311095</v>
+        <v>24.662419</v>
       </c>
       <c r="B107" t="n">
-        <v>16.343455</v>
+        <v>28.279252</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>14.110172</v>
+        <v>26.464627</v>
       </c>
       <c r="B108" t="n">
-        <v>16.782353</v>
+        <v>29.269125</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>14.909248</v>
+        <v>28.266836</v>
       </c>
       <c r="B109" t="n">
-        <v>17.217796</v>
+        <v>30.251209</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>15.708325</v>
+        <v>30.069044</v>
       </c>
       <c r="B110" t="n">
-        <v>17.649786</v>
+        <v>31.225504</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>16.507401</v>
+        <v>31.871253</v>
       </c>
       <c r="B111" t="n">
-        <v>18.078322</v>
+        <v>32.192009</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>17.306478</v>
+        <v>33.673461</v>
       </c>
       <c r="B112" t="n">
-        <v>18.503405</v>
+        <v>33.150725</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>18.105554</v>
+        <v>35.47567</v>
       </c>
       <c r="B113" t="n">
-        <v>18.925033</v>
+        <v>34.101651</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>18.904631</v>
+        <v>37.277878</v>
       </c>
       <c r="B114" t="n">
-        <v>19.343208</v>
+        <v>35.044787</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>19.703707</v>
+        <v>39.080087</v>
       </c>
       <c r="B115" t="n">
-        <v>19.757929</v>
+        <v>35.980134</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>20.502783</v>
+        <v>40.882296</v>
       </c>
       <c r="B116" t="n">
-        <v>20.169196</v>
+        <v>36.907691</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>21.30186</v>
+        <v>42.684504</v>
       </c>
       <c r="B117" t="n">
-        <v>20.57701</v>
+        <v>37.827459</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>22.100936</v>
+        <v>44.486713</v>
       </c>
       <c r="B118" t="n">
-        <v>20.981369</v>
+        <v>38.739437</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>22.900013</v>
+        <v>46.288921</v>
       </c>
       <c r="B119" t="n">
-        <v>21.382275</v>
+        <v>39.643626</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>23.699089</v>
+        <v>48.09113</v>
       </c>
       <c r="B120" t="n">
-        <v>21.779727</v>
+        <v>40.540025</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>24.498166</v>
+        <v>49.893338</v>
       </c>
       <c r="B121" t="n">
-        <v>22.173726</v>
+        <v>41.428635</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>25.297242</v>
+        <v>51.695547</v>
       </c>
       <c r="B122" t="n">
-        <v>22.56427</v>
+        <v>42.309455</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>26.096319</v>
+        <v>53.497755</v>
       </c>
       <c r="B123" t="n">
-        <v>22.951361</v>
+        <v>43.182486</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>26.895395</v>
+        <v>55.299964</v>
       </c>
       <c r="B124" t="n">
-        <v>23.334998</v>
+        <v>44.047727</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>27.694472</v>
+        <v>57.102172</v>
       </c>
       <c r="B125" t="n">
-        <v>23.715181</v>
+        <v>44.905179</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>28.493548</v>
+        <v>58.904381</v>
       </c>
       <c r="B126" t="n">
-        <v>24.09191</v>
+        <v>45.754841</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>29.292624</v>
+        <v>60.70659</v>
       </c>
       <c r="B127" t="n">
-        <v>24.465186</v>
+        <v>46.596713</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>30.091701</v>
+        <v>62.508798</v>
       </c>
       <c r="B128" t="n">
-        <v>24.835008</v>
+        <v>47.430796</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>30.890777</v>
+        <v>64.311007</v>
       </c>
       <c r="B129" t="n">
-        <v>25.201376</v>
+        <v>48.25709</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>31.689854</v>
+        <v>66.113215</v>
       </c>
       <c r="B130" t="n">
-        <v>25.56429</v>
+        <v>49.075593</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>32.48893</v>
+        <v>67.915424</v>
       </c>
       <c r="B131" t="n">
-        <v>25.923751</v>
+        <v>49.886308</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>33.288007</v>
+        <v>69.71763199999999</v>
       </c>
       <c r="B132" t="n">
-        <v>26.279757</v>
+        <v>50.689233</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>34.087083</v>
+        <v>71.519841</v>
       </c>
       <c r="B133" t="n">
-        <v>26.63231</v>
+        <v>51.484368</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>34.88616</v>
+        <v>73.32204900000001</v>
       </c>
       <c r="B134" t="n">
-        <v>26.981409</v>
+        <v>52.271714</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>35.685236</v>
+        <v>75.124258</v>
       </c>
       <c r="B135" t="n">
-        <v>27.327055</v>
+        <v>53.05127</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>36.484313</v>
+        <v>76.926466</v>
       </c>
       <c r="B136" t="n">
-        <v>27.669246</v>
+        <v>53.823037</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>37.283389</v>
+        <v>78.728675</v>
       </c>
       <c r="B137" t="n">
-        <v>28.007984</v>
+        <v>54.587014</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>38.082465</v>
+        <v>80.530883</v>
       </c>
       <c r="B138" t="n">
-        <v>28.343268</v>
+        <v>55.343202</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>38.881542</v>
+        <v>82.33309199999999</v>
       </c>
       <c r="B139" t="n">
-        <v>28.675098</v>
+        <v>56.0916</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>39.680618</v>
+        <v>84.135301</v>
       </c>
       <c r="B140" t="n">
-        <v>29.003475</v>
+        <v>56.832208</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>40.479695</v>
+        <v>85.93750900000001</v>
       </c>
       <c r="B141" t="n">
-        <v>29.328398</v>
+        <v>57.565027</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>41.278771</v>
+        <v>87.739718</v>
       </c>
       <c r="B142" t="n">
-        <v>29.649866</v>
+        <v>58.290057</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>42.077848</v>
+        <v>89.541926</v>
       </c>
       <c r="B143" t="n">
-        <v>29.967882</v>
+        <v>59.007297</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>42.876924</v>
+        <v>91.34413499999999</v>
       </c>
       <c r="B144" t="n">
-        <v>30.282443</v>
+        <v>59.716747</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>43.676001</v>
+        <v>93.146343</v>
       </c>
       <c r="B145" t="n">
-        <v>30.593551</v>
+        <v>60.418408</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>44.475077</v>
+        <v>94.94855200000001</v>
       </c>
       <c r="B146" t="n">
-        <v>30.901204</v>
+        <v>61.11228</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>45.274153</v>
+        <v>96.75076</v>
       </c>
       <c r="B147" t="n">
-        <v>31.205404</v>
+        <v>61.798361</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>46.07323</v>
+        <v>98.552969</v>
       </c>
       <c r="B148" t="n">
-        <v>31.506151</v>
+        <v>62.476654</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>46.872306</v>
+        <v>100.355177</v>
       </c>
       <c r="B149" t="n">
-        <v>31.803443</v>
+        <v>63.147157</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>47.671383</v>
+        <v>102.157386</v>
       </c>
       <c r="B150" t="n">
-        <v>32.097282</v>
+        <v>63.80987</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>48.470459</v>
+        <v>103.959594</v>
       </c>
       <c r="B151" t="n">
-        <v>32.387667</v>
+        <v>64.464794</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>49.269536</v>
+        <v>105.761803</v>
       </c>
       <c r="B152" t="n">
-        <v>32.674598</v>
+        <v>65.11192800000001</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>50.068612</v>
+        <v>107.564012</v>
       </c>
       <c r="B153" t="n">
-        <v>32.958075</v>
+        <v>65.751272</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>50.867689</v>
+        <v>109.36622</v>
       </c>
       <c r="B154" t="n">
-        <v>33.238099</v>
+        <v>66.382828</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>51.666765</v>
+        <v>111.168429</v>
       </c>
       <c r="B155" t="n">
-        <v>33.514668</v>
+        <v>67.006593</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>52.465842</v>
+        <v>112.970637</v>
       </c>
       <c r="B156" t="n">
-        <v>33.787784</v>
+        <v>67.622569</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>53.264918</v>
+        <v>114.772846</v>
       </c>
       <c r="B157" t="n">
-        <v>34.057447</v>
+        <v>68.230756</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>54.063994</v>
+        <v>116.575054</v>
       </c>
       <c r="B158" t="n">
-        <v>34.323655</v>
+        <v>68.831153</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>54.863071</v>
+        <v>118.377263</v>
       </c>
       <c r="B159" t="n">
-        <v>34.58641</v>
+        <v>69.42376</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>55.662147</v>
+        <v>120.179471</v>
       </c>
       <c r="B160" t="n">
-        <v>34.84571</v>
+        <v>70.008578</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>56.461224</v>
+        <v>121.98168</v>
       </c>
       <c r="B161" t="n">
-        <v>35.101558</v>
+        <v>70.585607</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>57.2603</v>
+        <v>123.783888</v>
       </c>
       <c r="B162" t="n">
-        <v>35.353951</v>
+        <v>71.15484499999999</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>58.059377</v>
+        <v>125.586097</v>
       </c>
       <c r="B163" t="n">
-        <v>35.60289</v>
+        <v>71.716295</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>58.858453</v>
+        <v>127.388306</v>
       </c>
       <c r="B164" t="n">
-        <v>35.848376</v>
+        <v>72.269955</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>59.65753</v>
+        <v>129.190514</v>
       </c>
       <c r="B165" t="n">
-        <v>36.090408</v>
+        <v>72.815825</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>60.456606</v>
+        <v>130.992723</v>
       </c>
       <c r="B166" t="n">
-        <v>36.328986</v>
+        <v>73.35390599999999</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>61.255683</v>
+        <v>132.794931</v>
       </c>
       <c r="B167" t="n">
-        <v>36.564111</v>
+        <v>73.884197</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>62.054759</v>
+        <v>134.59714</v>
       </c>
       <c r="B168" t="n">
-        <v>36.795781</v>
+        <v>74.40669800000001</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>62.853835</v>
+        <v>136.399348</v>
       </c>
       <c r="B169" t="n">
-        <v>37.023998</v>
+        <v>74.92141100000001</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>63.652912</v>
+        <v>138.201557</v>
       </c>
       <c r="B170" t="n">
-        <v>37.248761</v>
+        <v>75.42833299999999</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>64.451988</v>
+        <v>140.003765</v>
       </c>
       <c r="B171" t="n">
-        <v>37.470071</v>
+        <v>75.927466</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>65.251065</v>
+        <v>141.805974</v>
       </c>
       <c r="B172" t="n">
-        <v>37.687926</v>
+        <v>76.41880999999999</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>66.050141</v>
+        <v>143.608182</v>
       </c>
       <c r="B173" t="n">
-        <v>37.902328</v>
+        <v>76.90236400000001</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>66.84921799999999</v>
+        <v>145.410391</v>
       </c>
       <c r="B174" t="n">
-        <v>38.113276</v>
+        <v>77.378128</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>67.64829400000001</v>
+        <v>147.212599</v>
       </c>
       <c r="B175" t="n">
-        <v>38.32077</v>
+        <v>77.846103</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>68.447371</v>
+        <v>149.014808</v>
       </c>
       <c r="B176" t="n">
-        <v>38.52481</v>
+        <v>78.30628900000001</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>69.246447</v>
+        <v>150.817017</v>
       </c>
       <c r="B177" t="n">
-        <v>38.725397</v>
+        <v>78.758685</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>70.045524</v>
+        <v>152.619225</v>
       </c>
       <c r="B178" t="n">
-        <v>38.92253</v>
+        <v>79.20329099999999</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>70.8446</v>
+        <v>154.421434</v>
       </c>
       <c r="B179" t="n">
-        <v>39.116209</v>
+        <v>79.640108</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>71.643676</v>
+        <v>156.223642</v>
       </c>
       <c r="B180" t="n">
-        <v>39.306434</v>
+        <v>80.069135</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>72.442753</v>
+        <v>158.025851</v>
       </c>
       <c r="B181" t="n">
-        <v>39.493206</v>
+        <v>80.49037300000001</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>73.241829</v>
+        <v>159.828059</v>
       </c>
       <c r="B182" t="n">
-        <v>39.676523</v>
+        <v>80.90382099999999</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>74.04090600000001</v>
+        <v>161.630268</v>
       </c>
       <c r="B183" t="n">
-        <v>39.856387</v>
+        <v>81.30947999999999</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>74.83998200000001</v>
+        <v>163.432476</v>
       </c>
       <c r="B184" t="n">
-        <v>40.032797</v>
+        <v>81.70734899999999</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>75.639059</v>
+        <v>165.234685</v>
       </c>
       <c r="B185" t="n">
-        <v>40.205754</v>
+        <v>82.09742799999999</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>76.438135</v>
+        <v>167.036893</v>
       </c>
       <c r="B186" t="n">
-        <v>40.375256</v>
+        <v>82.479719</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>77.237212</v>
+        <v>168.839102</v>
       </c>
       <c r="B187" t="n">
-        <v>40.541305</v>
+        <v>82.854219</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>78.036288</v>
+        <v>170.641311</v>
       </c>
       <c r="B188" t="n">
-        <v>40.7039</v>
+        <v>83.22093</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>78.835365</v>
+        <v>172.443519</v>
       </c>
       <c r="B189" t="n">
-        <v>40.863041</v>
+        <v>83.579852</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>79.634441</v>
+        <v>174.245728</v>
       </c>
       <c r="B190" t="n">
-        <v>41.018729</v>
+        <v>83.930984</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>80.43351699999999</v>
+        <v>176.047936</v>
       </c>
       <c r="B191" t="n">
-        <v>41.170963</v>
+        <v>84.274326</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>81.23259400000001</v>
+        <v>177.850145</v>
       </c>
       <c r="B192" t="n">
-        <v>41.319742</v>
+        <v>84.60987900000001</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>82.03167000000001</v>
+        <v>179.652353</v>
       </c>
       <c r="B193" t="n">
-        <v>41.465069</v>
+        <v>84.937642</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>82.830747</v>
+        <v>181.454562</v>
       </c>
       <c r="B194" t="n">
-        <v>41.606941</v>
+        <v>85.257616</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>83.629823</v>
+        <v>183.25677</v>
       </c>
       <c r="B195" t="n">
-        <v>41.745359</v>
+        <v>85.5698</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>84.4289</v>
+        <v>185.058979</v>
       </c>
       <c r="B196" t="n">
-        <v>41.880324</v>
+        <v>85.874195</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>85.227976</v>
+        <v>186.861187</v>
       </c>
       <c r="B197" t="n">
-        <v>42.011835</v>
+        <v>86.1708</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>86.027053</v>
+        <v>188.663396</v>
       </c>
       <c r="B198" t="n">
-        <v>42.139892</v>
+        <v>86.459616</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>86.82612899999999</v>
+        <v>190.465604</v>
       </c>
       <c r="B199" t="n">
-        <v>42.264496</v>
+        <v>86.74064199999999</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>87.62520600000001</v>
+        <v>192.267813</v>
       </c>
       <c r="B200" t="n">
-        <v>42.385646</v>
+        <v>87.013879</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
